--- a/extenbooks/XS004_extenbook.xlsx
+++ b/extenbooks/XS004_extenbook.xlsx
@@ -764,7 +764,7 @@
         <v>1930</v>
       </c>
       <c r="B9" t="n">
-        <v>100.8094124963792</v>
+        <v>100.8094124963793</v>
       </c>
       <c r="C9" t="n">
         <v>183.9625949861598</v>
@@ -778,7 +778,7 @@
         <v>1931</v>
       </c>
       <c r="B10" t="n">
-        <v>95.23462549030228</v>
+        <v>95.23462549030229</v>
       </c>
       <c r="C10" t="n">
         <v>173.7894151338333</v>
@@ -792,7 +792,7 @@
         <v>1932</v>
       </c>
       <c r="B11" t="n">
-        <v>90.44385799890452</v>
+        <v>90.44385799890453</v>
       </c>
       <c r="C11" t="n">
         <v>165.0469574816322</v>
@@ -1002,7 +1002,7 @@
         <v>1947</v>
       </c>
       <c r="B26" t="n">
-        <v>93.47745529215312</v>
+        <v>93.47745529215311</v>
       </c>
       <c r="C26" t="n">
         <v>170.5828337097477</v>
@@ -1050,7 +1050,7 @@
         <v>230.2060065290138</v>
       </c>
       <c r="D29" t="n">
-        <v>98.16177380379636</v>
+        <v>98.16177380379635</v>
       </c>
     </row>
     <row r="30">
@@ -1064,7 +1064,7 @@
         <v>255.8497941460225</v>
       </c>
       <c r="D30" t="n">
-        <v>107.4617738037964</v>
+        <v>107.4617738037963</v>
       </c>
     </row>
     <row r="31">
@@ -1148,7 +1148,7 @@
         <v>426.5861093605473</v>
       </c>
       <c r="D36" t="n">
-        <v>189.7617738037964</v>
+        <v>189.7617738037963</v>
       </c>
     </row>
     <row r="37">
@@ -1159,10 +1159,10 @@
         <v>274.9129145816438</v>
       </c>
       <c r="C37" t="n">
-        <v>442.5900830932797</v>
+        <v>442.5900830932796</v>
       </c>
       <c r="D37" t="n">
-        <v>209.1617738037964</v>
+        <v>209.1617738037963</v>
       </c>
     </row>
     <row r="38">
@@ -1190,7 +1190,7 @@
         <v>484.9322528829036</v>
       </c>
       <c r="D39" t="n">
-        <v>237.2617738037964</v>
+        <v>237.2617738037963</v>
       </c>
     </row>
     <row r="40">
@@ -1313,7 +1313,7 @@
         <v>588.3750570199951</v>
       </c>
       <c r="C48" t="n">
-        <v>928.3262407092184</v>
+        <v>928.3262407092185</v>
       </c>
       <c r="D48" t="n">
         <v>462.1617738037963</v>
@@ -1467,7 +1467,7 @@
         <v>2311.278873253696</v>
       </c>
       <c r="C59" t="n">
-        <v>3800.071121600248</v>
+        <v>3800.071121600247</v>
       </c>
       <c r="D59" t="n">
         <v>1284.961773803796</v>
@@ -1478,7 +1478,7 @@
         <v>1981</v>
       </c>
       <c r="B60" t="n">
-        <v>2619.722347407632</v>
+        <v>2619.722347407631</v>
       </c>
       <c r="C60" t="n">
         <v>4326.983953050354</v>
@@ -1705,7 +1705,7 @@
         <v>6010.76351989286</v>
       </c>
       <c r="C76" t="n">
-        <v>10645.46761806426</v>
+        <v>10645.46761806427</v>
       </c>
       <c r="D76" t="n">
         <v>4538.161773803796</v>
@@ -1887,7 +1887,7 @@
         <v>11406.91836245093</v>
       </c>
       <c r="C89" t="n">
-        <v>21982.08196158393</v>
+        <v>21982.08196158394</v>
       </c>
       <c r="D89" t="n">
         <v>8701.361773803797</v>
@@ -1969,14 +1969,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B97" t="n">
-        <v>141.919</v>
+        <v>81.25391618497109</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1992,14 +1992,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B98" t="n">
-        <v>57.457</v>
+        <v>87.43775554517183</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2015,10 +2015,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="B99" t="n">
-        <v>81.25391618497109</v>
+        <v>91.59197584292994</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2038,14 +2038,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="B100" t="n">
-        <v>148.2766430635838</v>
+        <v>97.02012370492236</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2061,14 +2061,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="B101" t="n">
-        <v>60.03094075144509</v>
+        <v>100.8094124963793</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="B102" t="n">
-        <v>87.43775554517183</v>
+        <v>95.23462549030229</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2107,14 +2107,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="B103" t="n">
-        <v>159.5612553583032</v>
+        <v>90.44385799890453</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2130,14 +2130,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
       <c r="B104" t="n">
-        <v>64.59960293633712</v>
+        <v>87.44858684558716</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="B105" t="n">
-        <v>91.59197584292994</v>
+        <v>85.60976530584544</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2176,14 +2176,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1928</v>
+        <v>1935</v>
       </c>
       <c r="B106" t="n">
-        <v>167.1421064633249</v>
+        <v>83.71762044098207</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2199,14 +2199,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="B107" t="n">
-        <v>67.66876888269546</v>
+        <v>81.54552811923008</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="B108" t="n">
-        <v>97.02012370492236</v>
+        <v>83.58431212817798</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2245,14 +2245,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="B109" t="n">
-        <v>177.0476910901232</v>
+        <v>82.73363845709673</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2268,14 +2268,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="B110" t="n">
-        <v>71.67912109700045</v>
+        <v>83.50599349440556</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="B111" t="n">
-        <v>100.8094124963792</v>
+        <v>83.49599537094525</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2314,14 +2314,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1930</v>
+        <v>1941</v>
       </c>
       <c r="B112" t="n">
-        <v>183.9625949861598</v>
+        <v>83.89925301717768</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2337,14 +2337,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1930</v>
+        <v>1942</v>
       </c>
       <c r="B113" t="n">
-        <v>74.47867318766185</v>
+        <v>83.12773115682388</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2360,10 +2360,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1931</v>
+        <v>1943</v>
       </c>
       <c r="B114" t="n">
-        <v>95.23462549030228</v>
+        <v>81.42471746075137</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2383,14 +2383,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1931</v>
+        <v>1944</v>
       </c>
       <c r="B115" t="n">
-        <v>173.7894151338333</v>
+        <v>79.25845737768455</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2406,14 +2406,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="B116" t="n">
-        <v>70.35998298567957</v>
+        <v>76.69977094880063</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="B117" t="n">
-        <v>90.44385799890452</v>
+        <v>83.5918107207732</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2452,14 +2452,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="B118" t="n">
-        <v>165.0469574816322</v>
+        <v>93.47745529215311</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2475,14 +2475,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="B119" t="n">
-        <v>66.82053168372198</v>
+        <v>108.8718194723678</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="B120" t="n">
-        <v>87.44858684558716</v>
+        <v>116.342353914337</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2521,14 +2521,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1933</v>
+        <v>1950</v>
       </c>
       <c r="B121" t="n">
-        <v>159.5810209147343</v>
+        <v>135.4786434270008</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2544,14 +2544,14 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1933</v>
+        <v>1951</v>
       </c>
       <c r="B122" t="n">
-        <v>64.60760517406329</v>
+        <v>153.0501888352264</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2567,10 +2567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1934</v>
+        <v>1952</v>
       </c>
       <c r="B123" t="n">
-        <v>85.60976530584544</v>
+        <v>167.3506608107679</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2590,14 +2590,14 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1934</v>
+        <v>1953</v>
       </c>
       <c r="B124" t="n">
-        <v>156.2254376037068</v>
+        <v>181.0929233081971</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2613,14 +2613,14 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1934</v>
+        <v>1954</v>
       </c>
       <c r="B125" t="n">
-        <v>63.24907143085974</v>
+        <v>190.9591473281131</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1935</v>
+        <v>1955</v>
       </c>
       <c r="B126" t="n">
-        <v>83.71762044098207</v>
+        <v>214.4497476504858</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2659,14 +2659,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1935</v>
+        <v>1956</v>
       </c>
       <c r="B127" t="n">
-        <v>152.7725469379419</v>
+        <v>243.1735646598359</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2682,14 +2682,14 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1935</v>
+        <v>1957</v>
       </c>
       <c r="B128" t="n">
-        <v>61.85114205577353</v>
+        <v>266.0805277589744</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1936</v>
+        <v>1958</v>
       </c>
       <c r="B129" t="n">
-        <v>81.54552811923008</v>
+        <v>274.9129145816438</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2728,14 +2728,14 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1936</v>
+        <v>1959</v>
       </c>
       <c r="B130" t="n">
-        <v>148.8087926598047</v>
+        <v>290.5676639267082</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2751,14 +2751,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1936</v>
+        <v>1960</v>
       </c>
       <c r="B131" t="n">
-        <v>60.24638561330337</v>
+        <v>299.9965190841172</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1937</v>
+        <v>1961</v>
       </c>
       <c r="B132" t="n">
-        <v>83.58431212817798</v>
+        <v>310.3486750738687</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2797,14 +2797,14 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1937</v>
+        <v>1962</v>
       </c>
       <c r="B133" t="n">
-        <v>152.529278551098</v>
+        <v>323.6909055065932</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2820,14 +2820,14 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1937</v>
+        <v>1963</v>
       </c>
       <c r="B134" t="n">
-        <v>61.7526529760669</v>
+        <v>337.5669988584335</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1938</v>
+        <v>1964</v>
       </c>
       <c r="B135" t="n">
-        <v>82.73363845709673</v>
+        <v>360.6794565638425</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1938</v>
+        <v>1965</v>
       </c>
       <c r="B136" t="n">
-        <v>150.9769221575506</v>
+        <v>391.5198749168491</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2889,14 +2889,14 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1938</v>
+        <v>1966</v>
       </c>
       <c r="B137" t="n">
-        <v>61.12416953618886</v>
+        <v>433.0549898423711</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1939</v>
+        <v>1967</v>
       </c>
       <c r="B138" t="n">
-        <v>83.50599349440556</v>
+        <v>475.109465585575</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2935,14 +2935,14 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1939</v>
+        <v>1968</v>
       </c>
       <c r="B139" t="n">
-        <v>152.3863583738272</v>
+        <v>528.4643465621049</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2958,14 +2958,14 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1939</v>
+        <v>1969</v>
       </c>
       <c r="B140" t="n">
-        <v>61.69479064173924</v>
+        <v>588.3750570199951</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2981,10 +2981,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1940</v>
+        <v>1970</v>
       </c>
       <c r="B141" t="n">
-        <v>83.49599537094525</v>
+        <v>653.1706816834147</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3004,14 +3004,14 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1940</v>
+        <v>1971</v>
       </c>
       <c r="B142" t="n">
-        <v>152.3681132448139</v>
+        <v>721.3901275801234</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3027,14 +3027,14 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1940</v>
+        <v>1972</v>
       </c>
       <c r="B143" t="n">
-        <v>61.68740396076124</v>
+        <v>789.177136353478</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3050,10 +3050,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1941</v>
+        <v>1973</v>
       </c>
       <c r="B144" t="n">
-        <v>83.89925301717768</v>
+        <v>898.7857073762829</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3073,14 +3073,14 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1941</v>
+        <v>1974</v>
       </c>
       <c r="B145" t="n">
-        <v>153.1040001150166</v>
+        <v>1106.067269539726</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3096,14 +3096,14 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1941</v>
+        <v>1975</v>
       </c>
       <c r="B146" t="n">
-        <v>61.98533342687384</v>
+        <v>1233.086274487952</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1942</v>
+        <v>1976</v>
       </c>
       <c r="B147" t="n">
-        <v>83.12773115682388</v>
+        <v>1358.791779423558</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3142,14 +3142,14 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1942</v>
+        <v>1977</v>
       </c>
       <c r="B148" t="n">
-        <v>151.6960843261578</v>
+        <v>1517.933002689201</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3165,14 +3165,14 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1942</v>
+        <v>1978</v>
       </c>
       <c r="B149" t="n">
-        <v>61.41532787807163</v>
+        <v>1732.734766954208</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3188,10 +3188,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1943</v>
+        <v>1979</v>
       </c>
       <c r="B150" t="n">
-        <v>81.42471746075137</v>
+        <v>2003.806167187476</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1943</v>
+        <v>1980</v>
       </c>
       <c r="B151" t="n">
-        <v>148.5883306842275</v>
+        <v>2311.278873253696</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3234,14 +3234,14 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1943</v>
+        <v>1981</v>
       </c>
       <c r="B152" t="n">
-        <v>60.15712988481923</v>
+        <v>2619.722347407631</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1944</v>
+        <v>1982</v>
       </c>
       <c r="B153" t="n">
-        <v>79.25845737768455</v>
+        <v>2784.308591389185</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3280,14 +3280,14 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1944</v>
+        <v>1983</v>
       </c>
       <c r="B154" t="n">
-        <v>144.6352193980148</v>
+        <v>2868.04963575033</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3303,14 +3303,14 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1944</v>
+        <v>1984</v>
       </c>
       <c r="B155" t="n">
-        <v>58.55668233958623</v>
+        <v>3045.659459810445</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3326,10 +3326,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1945</v>
+        <v>1985</v>
       </c>
       <c r="B156" t="n">
-        <v>76.69977094880063</v>
+        <v>3224.884995537328</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3349,14 +3349,14 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1945</v>
+        <v>1986</v>
       </c>
       <c r="B157" t="n">
-        <v>139.9659867980306</v>
+        <v>3377.160104795191</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3372,14 +3372,14 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1945</v>
+        <v>1987</v>
       </c>
       <c r="B158" t="n">
-        <v>56.6663075659668</v>
+        <v>3558.127794149545</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1946</v>
+        <v>1988</v>
       </c>
       <c r="B159" t="n">
-        <v>83.5918107207732</v>
+        <v>3790.134292234051</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3418,14 +3418,14 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1946</v>
+        <v>1989</v>
       </c>
       <c r="B160" t="n">
-        <v>152.542962397858</v>
+        <v>4022.319996688179</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3441,14 +3441,14 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1946</v>
+        <v>1990</v>
       </c>
       <c r="B161" t="n">
-        <v>61.75819298680039</v>
+        <v>4263.947225064116</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1947</v>
+        <v>1991</v>
       </c>
       <c r="B162" t="n">
-        <v>93.47745529215312</v>
+        <v>4375.666147815624</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3487,14 +3487,14 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B163" t="n">
-        <v>170.5828337097477</v>
+        <v>4534.086319000641</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3510,14 +3510,14 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1947</v>
+        <v>1993</v>
       </c>
       <c r="B164" t="n">
-        <v>69.06177380379634</v>
+        <v>4760.179144740486</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1948</v>
+        <v>1994</v>
       </c>
       <c r="B165" t="n">
-        <v>108.8718194723678</v>
+        <v>5039.103609611528</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3556,14 +3556,14 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1948</v>
+        <v>1995</v>
       </c>
       <c r="B166" t="n">
-        <v>191.6835928065198</v>
+        <v>5352.00432043499</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3579,14 +3579,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1948</v>
+        <v>1996</v>
       </c>
       <c r="B167" t="n">
-        <v>78.76177380379634</v>
+        <v>5657.812458290044</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1949</v>
+        <v>1997</v>
       </c>
       <c r="B168" t="n">
-        <v>116.342353914337</v>
+        <v>6010.76351989286</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3625,14 +3625,14 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1949</v>
+        <v>1998</v>
       </c>
       <c r="B169" t="n">
-        <v>200.7047696097666</v>
+        <v>6392.930342530286</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3648,14 +3648,14 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1949</v>
+        <v>1999</v>
       </c>
       <c r="B170" t="n">
-        <v>89.66177380379635</v>
+        <v>6820.809694788109</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="B171" t="n">
-        <v>135.4786434270008</v>
+        <v>7358.470947300596</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3694,14 +3694,14 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="B172" t="n">
-        <v>230.2060065290138</v>
+        <v>7789.9967768644</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3717,14 +3717,14 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1950</v>
+        <v>2002</v>
       </c>
       <c r="B173" t="n">
-        <v>98.16177380379636</v>
+        <v>8079.863475494672</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1951</v>
+        <v>2003</v>
       </c>
       <c r="B174" t="n">
-        <v>153.0501888352264</v>
+        <v>8328.17365576649</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -3763,14 +3763,14 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1951</v>
+        <v>2004</v>
       </c>
       <c r="B175" t="n">
-        <v>255.8497941460225</v>
+        <v>8958.441220393472</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3786,14 +3786,14 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1951</v>
+        <v>2005</v>
       </c>
       <c r="B176" t="n">
-        <v>107.4617738037964</v>
+        <v>9708.448126981471</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1952</v>
+        <v>2006</v>
       </c>
       <c r="B177" t="n">
-        <v>167.3506608107679</v>
+        <v>10478.50360494466</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3832,14 +3832,14 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1952</v>
+        <v>2007</v>
       </c>
       <c r="B178" t="n">
-        <v>276.7328418152084</v>
+        <v>11015.54514157127</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3855,14 +3855,14 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1952</v>
+        <v>2008</v>
       </c>
       <c r="B179" t="n">
-        <v>119.8617738037964</v>
+        <v>11694.58088462759</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3878,10 +3878,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1953</v>
+        <v>2009</v>
       </c>
       <c r="B180" t="n">
-        <v>181.0929233081971</v>
+        <v>11238.49963090679</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -3901,14 +3901,14 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1953</v>
+        <v>2010</v>
       </c>
       <c r="B181" t="n">
-        <v>296.535558486477</v>
+        <v>11406.91836245093</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3924,14 +3924,14 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1953</v>
+        <v>2011</v>
       </c>
       <c r="B182" t="n">
-        <v>132.4617738037963</v>
+        <v>11797.97007262885</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3947,14 +3947,14 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1954</v>
+        <v>1925</v>
       </c>
       <c r="B183" t="n">
-        <v>190.9591473281131</v>
+        <v>141.919</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1954</v>
+        <v>1926</v>
       </c>
       <c r="B184" t="n">
-        <v>311.2351026905877</v>
+        <v>148.2766430635838</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3993,14 +3993,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1954</v>
+        <v>1927</v>
       </c>
       <c r="B185" t="n">
-        <v>146.1617738037963</v>
+        <v>159.5612553583032</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4016,14 +4016,14 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1955</v>
+        <v>1928</v>
       </c>
       <c r="B186" t="n">
-        <v>214.4497476504858</v>
+        <v>167.1421064633249</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1955</v>
+        <v>1929</v>
       </c>
       <c r="B187" t="n">
-        <v>347.9833912572905</v>
+        <v>177.0476910901232</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4062,14 +4062,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1955</v>
+        <v>1930</v>
       </c>
       <c r="B188" t="n">
-        <v>158.1617738037963</v>
+        <v>183.9625949861598</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4085,14 +4085,14 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1956</v>
+        <v>1931</v>
       </c>
       <c r="B189" t="n">
-        <v>243.1735646598359</v>
+        <v>173.7894151338333</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4108,10 +4108,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1956</v>
+        <v>1932</v>
       </c>
       <c r="B190" t="n">
-        <v>391.8473726280085</v>
+        <v>165.0469574816322</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4131,14 +4131,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1956</v>
+        <v>1933</v>
       </c>
       <c r="B191" t="n">
-        <v>171.7617738037963</v>
+        <v>159.5810209147343</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4154,14 +4154,14 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1957</v>
+        <v>1934</v>
       </c>
       <c r="B192" t="n">
-        <v>266.0805277589744</v>
+        <v>156.2254376037068</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4177,10 +4177,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1957</v>
+        <v>1935</v>
       </c>
       <c r="B193" t="n">
-        <v>426.5861093605473</v>
+        <v>152.7725469379419</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4200,14 +4200,14 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1957</v>
+        <v>1936</v>
       </c>
       <c r="B194" t="n">
-        <v>189.7617738037964</v>
+        <v>148.8087926598047</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4223,14 +4223,14 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1958</v>
+        <v>1937</v>
       </c>
       <c r="B195" t="n">
-        <v>274.9129145816438</v>
+        <v>152.529278551098</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4246,10 +4246,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1958</v>
+        <v>1938</v>
       </c>
       <c r="B196" t="n">
-        <v>442.5900830932797</v>
+        <v>150.9769221575506</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -4269,14 +4269,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1958</v>
+        <v>1939</v>
       </c>
       <c r="B197" t="n">
-        <v>209.1617738037964</v>
+        <v>152.3863583738272</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4292,14 +4292,14 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1959</v>
+        <v>1940</v>
       </c>
       <c r="B198" t="n">
-        <v>290.5676639267082</v>
+        <v>152.3681132448139</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1959</v>
+        <v>1941</v>
       </c>
       <c r="B199" t="n">
-        <v>469.2512596112735</v>
+        <v>153.1040001150166</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1959</v>
+        <v>1942</v>
       </c>
       <c r="B200" t="n">
-        <v>222.3617738037963</v>
+        <v>151.6960843261578</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4361,14 +4361,14 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1960</v>
+        <v>1943</v>
       </c>
       <c r="B201" t="n">
-        <v>299.9965190841172</v>
+        <v>148.5883306842275</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4384,10 +4384,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1960</v>
+        <v>1944</v>
       </c>
       <c r="B202" t="n">
-        <v>484.9322528829036</v>
+        <v>144.6352193980148</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -4407,14 +4407,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1960</v>
+        <v>1945</v>
       </c>
       <c r="B203" t="n">
-        <v>237.2617738037964</v>
+        <v>139.9659867980306</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4430,14 +4430,14 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1961</v>
+        <v>1946</v>
       </c>
       <c r="B204" t="n">
-        <v>310.3486750738687</v>
+        <v>152.542962397858</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4453,10 +4453,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1961</v>
+        <v>1947</v>
       </c>
       <c r="B205" t="n">
-        <v>503.2776347160874</v>
+        <v>170.5828337097477</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4476,14 +4476,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1961</v>
+        <v>1948</v>
       </c>
       <c r="B206" t="n">
-        <v>254.3617738037963</v>
+        <v>191.6835928065198</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4499,14 +4499,14 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1962</v>
+        <v>1949</v>
       </c>
       <c r="B207" t="n">
-        <v>323.6909055065932</v>
+        <v>200.7047696097666</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4522,10 +4522,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1962</v>
+        <v>1950</v>
       </c>
       <c r="B208" t="n">
-        <v>525.4492389980019</v>
+        <v>230.2060065290138</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -4545,14 +4545,14 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1962</v>
+        <v>1951</v>
       </c>
       <c r="B209" t="n">
-        <v>269.9617738037963</v>
+        <v>255.8497941460225</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4568,14 +4568,14 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1963</v>
+        <v>1952</v>
       </c>
       <c r="B210" t="n">
-        <v>337.5669988584335</v>
+        <v>276.7328418152084</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4591,10 +4591,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1963</v>
+        <v>1953</v>
       </c>
       <c r="B211" t="n">
-        <v>548.4317201515985</v>
+        <v>296.535558486477</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -4614,14 +4614,14 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1963</v>
+        <v>1954</v>
       </c>
       <c r="B212" t="n">
-        <v>287.4617738037963</v>
+        <v>311.2351026905877</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -4637,14 +4637,14 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1964</v>
+        <v>1955</v>
       </c>
       <c r="B213" t="n">
-        <v>360.6794565638425</v>
+        <v>347.9833912572905</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -4660,10 +4660,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1964</v>
+        <v>1956</v>
       </c>
       <c r="B214" t="n">
-        <v>584.416740608418</v>
+        <v>391.8473726280085</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4683,14 +4683,14 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1964</v>
+        <v>1957</v>
       </c>
       <c r="B215" t="n">
-        <v>305.6617738037963</v>
+        <v>426.5861093605473</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -4706,14 +4706,14 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1965</v>
+        <v>1958</v>
       </c>
       <c r="B216" t="n">
-        <v>391.5198749168491</v>
+        <v>442.5900830932796</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4729,10 +4729,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1965</v>
+        <v>1959</v>
       </c>
       <c r="B217" t="n">
-        <v>629.5138499735924</v>
+        <v>469.2512596112735</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -4752,14 +4752,14 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="B218" t="n">
-        <v>327.9617738037963</v>
+        <v>484.9322528829036</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -4775,14 +4775,14 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="B219" t="n">
-        <v>433.0549898423711</v>
+        <v>503.2776347160874</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -4798,10 +4798,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="B220" t="n">
-        <v>689.3389442732511</v>
+        <v>525.4492389980019</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -4821,14 +4821,14 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B221" t="n">
-        <v>357.0617738037964</v>
+        <v>548.4317201515985</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -4844,14 +4844,14 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="B222" t="n">
-        <v>475.109465585575</v>
+        <v>584.416740608418</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B223" t="n">
-        <v>753.3311352268145</v>
+        <v>629.5138499735924</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B224" t="n">
-        <v>392.1617738037963</v>
+        <v>689.3389442732511</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -4913,14 +4913,14 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B225" t="n">
-        <v>528.4643465621049</v>
+        <v>753.3311352268145</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -4959,14 +4959,14 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B227" t="n">
-        <v>425.5617738037963</v>
+        <v>928.3262407092185</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -4982,14 +4982,14 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B228" t="n">
-        <v>588.3750570199951</v>
+        <v>1032.410989618403</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5005,10 +5005,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B229" t="n">
-        <v>928.3262407092184</v>
+        <v>1145.856447448968</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -5028,14 +5028,14 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B230" t="n">
-        <v>462.1617738037963</v>
+        <v>1256.316688096983</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5051,14 +5051,14 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="B231" t="n">
-        <v>653.1706816834147</v>
+        <v>1429.560018309616</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="B232" t="n">
-        <v>1032.410989618403</v>
+        <v>1763.589689371715</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -5097,14 +5097,14 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="B233" t="n">
-        <v>503.6617738037963</v>
+        <v>1983.040821726274</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5120,14 +5120,14 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="B234" t="n">
-        <v>721.3901275801234</v>
+        <v>2204.961979321552</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="B235" t="n">
-        <v>1145.856447448968</v>
+        <v>2477.822211640865</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -5166,14 +5166,14 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="B236" t="n">
-        <v>543.9617738037963</v>
+        <v>2835.834184592632</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5189,14 +5189,14 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="B237" t="n">
-        <v>789.177136353478</v>
+        <v>3283.947207948604</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5212,10 +5212,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="B238" t="n">
-        <v>1256.316688096983</v>
+        <v>3800.071121600247</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -5235,14 +5235,14 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="B239" t="n">
-        <v>584.2617738037962</v>
+        <v>4326.983953050354</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5258,14 +5258,14 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="B240" t="n">
-        <v>898.7857073762829</v>
+        <v>4638.957776099302</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="B241" t="n">
-        <v>1429.560018309616</v>
+        <v>4822.675106371553</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -5304,14 +5304,14 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="B242" t="n">
-        <v>632.1617738037962</v>
+        <v>5136.971843292613</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5327,14 +5327,14 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="B243" t="n">
-        <v>1106.067269539726</v>
+        <v>5450.733993443455</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5350,10 +5350,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="B244" t="n">
-        <v>1763.589689371715</v>
+        <v>5739.714132823804</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -5373,14 +5373,14 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1974</v>
+        <v>1987</v>
       </c>
       <c r="B245" t="n">
-        <v>693.1617738037962</v>
+        <v>6092.19642781637</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5396,14 +5396,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1975</v>
+        <v>1988</v>
       </c>
       <c r="B246" t="n">
-        <v>1233.086274487952</v>
+        <v>6531.132870828345</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5419,10 +5419,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="B247" t="n">
-        <v>1983.040821726274</v>
+        <v>6967.269512947614</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -5442,14 +5442,14 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1975</v>
+        <v>1990</v>
       </c>
       <c r="B248" t="n">
-        <v>764.6617738037962</v>
+        <v>7416.819551621183</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5465,14 +5465,14 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1976</v>
+        <v>1991</v>
       </c>
       <c r="B249" t="n">
-        <v>1358.791779423558</v>
+        <v>7670.814119372146</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1976</v>
+        <v>1992</v>
       </c>
       <c r="B250" t="n">
-        <v>2204.961979321552</v>
+        <v>8013.034801142843</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -5511,14 +5511,14 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1976</v>
+        <v>1993</v>
       </c>
       <c r="B251" t="n">
-        <v>832.9617738037962</v>
+        <v>8456.679308939059</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5534,14 +5534,14 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1977</v>
+        <v>1994</v>
       </c>
       <c r="B252" t="n">
-        <v>1517.933002689201</v>
+        <v>8977.803393596974</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5557,10 +5557,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1977</v>
+        <v>1995</v>
       </c>
       <c r="B253" t="n">
-        <v>2477.822211640865</v>
+        <v>9530.432697032011</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -5580,14 +5580,14 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1977</v>
+        <v>1996</v>
       </c>
       <c r="B254" t="n">
-        <v>909.1617738037962</v>
+        <v>10053.44780274493</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -5603,14 +5603,14 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1978</v>
+        <v>1997</v>
       </c>
       <c r="B255" t="n">
-        <v>1732.734766954208</v>
+        <v>10645.46761806427</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -5626,10 +5626,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1978</v>
+        <v>1998</v>
       </c>
       <c r="B256" t="n">
-        <v>2835.834184592632</v>
+        <v>11273.09106570743</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -5649,14 +5649,14 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1978</v>
+        <v>1999</v>
       </c>
       <c r="B257" t="n">
-        <v>1005.361773803796</v>
+        <v>11967.66739653786</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -5672,14 +5672,14 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1979</v>
+        <v>2000</v>
       </c>
       <c r="B258" t="n">
-        <v>2003.806167187476</v>
+        <v>12840.56665694134</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5695,10 +5695,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="B259" t="n">
-        <v>3283.947207948604</v>
+        <v>13620.73316634319</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5718,14 +5718,14 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1979</v>
+        <v>2002</v>
       </c>
       <c r="B260" t="n">
-        <v>1131.261773803796</v>
+        <v>14281.23387252014</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5741,14 +5741,14 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="B261" t="n">
-        <v>2311.278873253696</v>
+        <v>14892.47915343409</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1980</v>
+        <v>2004</v>
       </c>
       <c r="B262" t="n">
-        <v>3800.071121600248</v>
+        <v>16199.66010837774</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -5787,14 +5787,14 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1980</v>
+        <v>2005</v>
       </c>
       <c r="B263" t="n">
-        <v>1284.961773803796</v>
+        <v>17723.46235535809</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -5810,14 +5810,14 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1981</v>
+        <v>2006</v>
       </c>
       <c r="B264" t="n">
-        <v>2619.722347407632</v>
+        <v>19265.16196987102</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -5833,10 +5833,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1981</v>
+        <v>2007</v>
       </c>
       <c r="B265" t="n">
-        <v>4326.983953050354</v>
+        <v>20353.55816995345</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -5856,14 +5856,14 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1981</v>
+        <v>2008</v>
       </c>
       <c r="B266" t="n">
-        <v>1449.061773803796</v>
+        <v>21776.88577520748</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -5879,14 +5879,14 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1982</v>
+        <v>2009</v>
       </c>
       <c r="B267" t="n">
-        <v>2784.308591389185</v>
+        <v>21294.71904053759</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -5902,10 +5902,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1982</v>
+        <v>2010</v>
       </c>
       <c r="B268" t="n">
-        <v>4638.957776099302</v>
+        <v>21982.08196158394</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -5925,14 +5925,14 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1982</v>
+        <v>2011</v>
       </c>
       <c r="B269" t="n">
-        <v>1636.861773803796</v>
+        <v>23023.96860235302</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>XS004-C</t>
+          <t>XS004-B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5948,14 +5948,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1983</v>
+        <v>1925</v>
       </c>
       <c r="B270" t="n">
-        <v>2868.04963575033</v>
+        <v>57.457</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5971,14 +5971,14 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1983</v>
+        <v>1926</v>
       </c>
       <c r="B271" t="n">
-        <v>4822.675106371553</v>
+        <v>60.03094075144509</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -5994,10 +5994,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1983</v>
+        <v>1927</v>
       </c>
       <c r="B272" t="n">
-        <v>1809.161773803796</v>
+        <v>64.59960293633712</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -6017,14 +6017,14 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1984</v>
+        <v>1928</v>
       </c>
       <c r="B273" t="n">
-        <v>3045.659459810445</v>
+        <v>67.66876888269546</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6040,14 +6040,14 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1984</v>
+        <v>1929</v>
       </c>
       <c r="B274" t="n">
-        <v>5136.971843292613</v>
+        <v>71.67912109700045</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6063,10 +6063,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1984</v>
+        <v>1930</v>
       </c>
       <c r="B275" t="n">
-        <v>1961.861773803796</v>
+        <v>74.47867318766185</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -6086,14 +6086,14 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1985</v>
+        <v>1931</v>
       </c>
       <c r="B276" t="n">
-        <v>3224.884995537328</v>
+        <v>70.35998298567957</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6109,14 +6109,14 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1985</v>
+        <v>1932</v>
       </c>
       <c r="B277" t="n">
-        <v>5450.733993443455</v>
+        <v>66.82053168372198</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1985</v>
+        <v>1933</v>
       </c>
       <c r="B278" t="n">
-        <v>2156.561773803796</v>
+        <v>64.60760517406329</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -6155,14 +6155,14 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1986</v>
+        <v>1934</v>
       </c>
       <c r="B279" t="n">
-        <v>3377.160104795191</v>
+        <v>63.24907143085974</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6178,14 +6178,14 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1986</v>
+        <v>1935</v>
       </c>
       <c r="B280" t="n">
-        <v>5739.714132823804</v>
+        <v>61.85114205577353</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6201,10 +6201,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1986</v>
+        <v>1936</v>
       </c>
       <c r="B281" t="n">
-        <v>2358.461773803796</v>
+        <v>60.24638561330337</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -6224,14 +6224,14 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1987</v>
+        <v>1937</v>
       </c>
       <c r="B282" t="n">
-        <v>3558.127794149545</v>
+        <v>61.7526529760669</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6247,14 +6247,14 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1987</v>
+        <v>1938</v>
       </c>
       <c r="B283" t="n">
-        <v>6092.19642781637</v>
+        <v>61.12416953618886</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1987</v>
+        <v>1939</v>
       </c>
       <c r="B284" t="n">
-        <v>2531.361773803796</v>
+        <v>61.69479064173924</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -6293,14 +6293,14 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1988</v>
+        <v>1940</v>
       </c>
       <c r="B285" t="n">
-        <v>3790.134292234051</v>
+        <v>61.68740396076124</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6316,14 +6316,14 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1988</v>
+        <v>1941</v>
       </c>
       <c r="B286" t="n">
-        <v>6531.132870828345</v>
+        <v>61.98533342687384</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6339,10 +6339,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1988</v>
+        <v>1942</v>
       </c>
       <c r="B287" t="n">
-        <v>2687.361773803796</v>
+        <v>61.41532787807163</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -6362,14 +6362,14 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1989</v>
+        <v>1943</v>
       </c>
       <c r="B288" t="n">
-        <v>4022.319996688179</v>
+        <v>60.15712988481923</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6385,14 +6385,14 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1989</v>
+        <v>1944</v>
       </c>
       <c r="B289" t="n">
-        <v>6967.269512947614</v>
+        <v>58.55668233958623</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6408,10 +6408,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1989</v>
+        <v>1945</v>
       </c>
       <c r="B290" t="n">
-        <v>2856.061773803796</v>
+        <v>56.6663075659668</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -6431,14 +6431,14 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1990</v>
+        <v>1946</v>
       </c>
       <c r="B291" t="n">
-        <v>4263.947225064116</v>
+        <v>61.75819298680039</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6454,14 +6454,14 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1990</v>
+        <v>1947</v>
       </c>
       <c r="B292" t="n">
-        <v>7416.819551621183</v>
+        <v>69.06177380379634</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6477,10 +6477,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1990</v>
+        <v>1948</v>
       </c>
       <c r="B293" t="n">
-        <v>3044.261773803796</v>
+        <v>78.76177380379634</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -6500,14 +6500,14 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1991</v>
+        <v>1949</v>
       </c>
       <c r="B294" t="n">
-        <v>4375.666147815624</v>
+        <v>89.66177380379635</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6523,14 +6523,14 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1991</v>
+        <v>1950</v>
       </c>
       <c r="B295" t="n">
-        <v>7670.814119372146</v>
+        <v>98.16177380379635</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6546,10 +6546,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1991</v>
+        <v>1951</v>
       </c>
       <c r="B296" t="n">
-        <v>3243.761773803796</v>
+        <v>107.4617738037963</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -6569,14 +6569,14 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1992</v>
+        <v>1952</v>
       </c>
       <c r="B297" t="n">
-        <v>4534.086319000641</v>
+        <v>119.8617738037964</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6592,14 +6592,14 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1992</v>
+        <v>1953</v>
       </c>
       <c r="B298" t="n">
-        <v>8013.034801142843</v>
+        <v>132.4617738037963</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6615,10 +6615,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1992</v>
+        <v>1954</v>
       </c>
       <c r="B299" t="n">
-        <v>3406.661773803796</v>
+        <v>146.1617738037963</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -6638,14 +6638,14 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1993</v>
+        <v>1955</v>
       </c>
       <c r="B300" t="n">
-        <v>4760.179144740486</v>
+        <v>158.1617738037963</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6661,14 +6661,14 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1993</v>
+        <v>1956</v>
       </c>
       <c r="B301" t="n">
-        <v>8456.679308939059</v>
+        <v>171.7617738037963</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -6684,10 +6684,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="B302" t="n">
-        <v>3567.161773803796</v>
+        <v>189.7617738037963</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -6707,14 +6707,14 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1994</v>
+        <v>1958</v>
       </c>
       <c r="B303" t="n">
-        <v>5039.103609611528</v>
+        <v>209.1617738037963</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6730,14 +6730,14 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1994</v>
+        <v>1959</v>
       </c>
       <c r="B304" t="n">
-        <v>8977.803393596974</v>
+        <v>222.3617738037963</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6753,10 +6753,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1994</v>
+        <v>1960</v>
       </c>
       <c r="B305" t="n">
-        <v>3758.361773803796</v>
+        <v>237.2617738037963</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -6776,14 +6776,14 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1995</v>
+        <v>1961</v>
       </c>
       <c r="B306" t="n">
-        <v>5352.00432043499</v>
+        <v>254.3617738037963</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -6799,14 +6799,14 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1995</v>
+        <v>1962</v>
       </c>
       <c r="B307" t="n">
-        <v>9530.432697032011</v>
+        <v>269.9617738037963</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1995</v>
+        <v>1963</v>
       </c>
       <c r="B308" t="n">
-        <v>3979.961773803796</v>
+        <v>287.4617738037963</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -6845,14 +6845,14 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1996</v>
+        <v>1964</v>
       </c>
       <c r="B309" t="n">
-        <v>5657.812458290044</v>
+        <v>305.6617738037963</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6868,14 +6868,14 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1996</v>
+        <v>1965</v>
       </c>
       <c r="B310" t="n">
-        <v>10053.44780274493</v>
+        <v>327.9617738037963</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6891,10 +6891,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1996</v>
+        <v>1966</v>
       </c>
       <c r="B311" t="n">
-        <v>4245.961773803796</v>
+        <v>357.0617738037964</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6914,14 +6914,14 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>1997</v>
+        <v>1967</v>
       </c>
       <c r="B312" t="n">
-        <v>6010.76351989286</v>
+        <v>392.1617738037963</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6937,14 +6937,14 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1997</v>
+        <v>1968</v>
       </c>
       <c r="B313" t="n">
-        <v>10645.46761806426</v>
+        <v>425.5617738037963</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -6960,10 +6960,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1997</v>
+        <v>1969</v>
       </c>
       <c r="B314" t="n">
-        <v>4538.161773803796</v>
+        <v>462.1617738037963</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -6983,14 +6983,14 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="B315" t="n">
-        <v>6392.930342530286</v>
+        <v>503.6617738037963</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7006,14 +7006,14 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1998</v>
+        <v>1971</v>
       </c>
       <c r="B316" t="n">
-        <v>11273.09106570743</v>
+        <v>543.9617738037963</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7029,10 +7029,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="B317" t="n">
-        <v>4855.761773803796</v>
+        <v>584.2617738037962</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -7052,14 +7052,14 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1999</v>
+        <v>1973</v>
       </c>
       <c r="B318" t="n">
-        <v>6820.809694788109</v>
+        <v>632.1617738037962</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7075,14 +7075,14 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1999</v>
+        <v>1974</v>
       </c>
       <c r="B319" t="n">
-        <v>11967.66739653786</v>
+        <v>693.1617738037962</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1999</v>
+        <v>1975</v>
       </c>
       <c r="B320" t="n">
-        <v>5200.061773803796</v>
+        <v>764.6617738037962</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -7121,14 +7121,14 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2000</v>
+        <v>1976</v>
       </c>
       <c r="B321" t="n">
-        <v>7358.470947300596</v>
+        <v>832.9617738037962</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7144,14 +7144,14 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2000</v>
+        <v>1977</v>
       </c>
       <c r="B322" t="n">
-        <v>12840.56665694134</v>
+        <v>909.1617738037962</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7167,10 +7167,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2000</v>
+        <v>1978</v>
       </c>
       <c r="B323" t="n">
-        <v>5571.061773803796</v>
+        <v>1005.361773803796</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -7190,14 +7190,14 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2001</v>
+        <v>1979</v>
       </c>
       <c r="B324" t="n">
-        <v>7789.9967768644</v>
+        <v>1131.261773803796</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7213,14 +7213,14 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2001</v>
+        <v>1980</v>
       </c>
       <c r="B325" t="n">
-        <v>13620.73316634319</v>
+        <v>1284.961773803796</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7236,10 +7236,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2001</v>
+        <v>1981</v>
       </c>
       <c r="B326" t="n">
-        <v>5981.461773803796</v>
+        <v>1449.061773803796</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -7259,14 +7259,14 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2002</v>
+        <v>1982</v>
       </c>
       <c r="B327" t="n">
-        <v>8079.863475494672</v>
+        <v>1636.861773803796</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7282,14 +7282,14 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="B328" t="n">
-        <v>14281.23387252014</v>
+        <v>1809.161773803796</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7305,10 +7305,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="B329" t="n">
-        <v>6304.461773803796</v>
+        <v>1961.861773803796</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -7328,14 +7328,14 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="B330" t="n">
-        <v>8328.17365576649</v>
+        <v>2156.561773803796</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7351,14 +7351,14 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2003</v>
+        <v>1986</v>
       </c>
       <c r="B331" t="n">
-        <v>14892.47915343409</v>
+        <v>2358.461773803796</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7374,10 +7374,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2003</v>
+        <v>1987</v>
       </c>
       <c r="B332" t="n">
-        <v>6497.761773803796</v>
+        <v>2531.361773803796</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -7397,14 +7397,14 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>2004</v>
+        <v>1988</v>
       </c>
       <c r="B333" t="n">
-        <v>8958.441220393472</v>
+        <v>2687.361773803796</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7420,14 +7420,14 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="B334" t="n">
-        <v>16199.66010837774</v>
+        <v>2856.061773803796</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7443,10 +7443,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="B335" t="n">
-        <v>6682.461773803796</v>
+        <v>3044.261773803796</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -7466,14 +7466,14 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="B336" t="n">
-        <v>9708.448126981471</v>
+        <v>3243.761773803796</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7489,14 +7489,14 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="B337" t="n">
-        <v>17723.46235535809</v>
+        <v>3406.661773803796</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="B338" t="n">
-        <v>6914.561773803796</v>
+        <v>3567.161773803796</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -7535,14 +7535,14 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>2006</v>
+        <v>1994</v>
       </c>
       <c r="B339" t="n">
-        <v>10478.50360494466</v>
+        <v>3758.361773803796</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7558,14 +7558,14 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="B340" t="n">
-        <v>19265.16196987102</v>
+        <v>3979.961773803796</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7581,10 +7581,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="B341" t="n">
-        <v>7225.361773803796</v>
+        <v>4245.961773803796</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -7604,14 +7604,14 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="B342" t="n">
-        <v>11015.54514157127</v>
+        <v>4538.161773803796</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7627,14 +7627,14 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="B343" t="n">
-        <v>20353.55816995345</v>
+        <v>4855.761773803796</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7650,10 +7650,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B344" t="n">
-        <v>7629.661773803797</v>
+        <v>5200.061773803796</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -7673,14 +7673,14 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B345" t="n">
-        <v>11694.58088462759</v>
+        <v>5571.061773803796</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7696,14 +7696,14 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="B346" t="n">
-        <v>21776.88577520748</v>
+        <v>5981.461773803796</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -7719,10 +7719,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="B347" t="n">
-        <v>8093.061773803796</v>
+        <v>6304.461773803796</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -7742,14 +7742,14 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="B348" t="n">
-        <v>11238.49963090679</v>
+        <v>6497.761773803796</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -7765,14 +7765,14 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="B349" t="n">
-        <v>21294.71904053759</v>
+        <v>6682.461773803796</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -7788,10 +7788,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B350" t="n">
-        <v>8536.261773803797</v>
+        <v>6914.561773803796</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -7811,14 +7811,14 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B351" t="n">
-        <v>11406.91836245093</v>
+        <v>7225.361773803796</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7834,14 +7834,14 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B352" t="n">
-        <v>21982.08196158393</v>
+        <v>7629.661773803797</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7857,10 +7857,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B353" t="n">
-        <v>8701.361773803797</v>
+        <v>8093.061773803796</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -7880,14 +7880,14 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B354" t="n">
-        <v>11797.97007262885</v>
+        <v>8536.261773803797</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>XS004-A</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7903,14 +7903,14 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B355" t="n">
-        <v>23023.96860235302</v>
+        <v>8701.361773803797</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>XS004-B</t>
+          <t>XS004-C</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8035,7 +8035,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Operational baseline used by S601-S604 (combines BEA 2011 initial + BEA 1993 depreciation + IRS interwar adjustment). Source: Appendix Table 6.8.II.5. Per Decision 0002 + Phase 4 Q6: XS004 is the operational baseline; XS005 is the pure reference. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Operational baseline used by S601-S604 (combines the BEA 2011 initial value, the BEA 1993 depreciation rates, and the IRS interwar adjustment). Source: Appendix Table 6.8.II.5. This series is the operational baseline used throughout Chapter 6; its companion series XS005 is the pure Generalized Perpetual Inventory Method (GPIM) reference.</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau (Historical Statistics 1975, for IRS book values), and the Federal Reserve Board G.17 industrial-production release (FRB G.17). All public domain.</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KNCcorp_baseline = GPIM (eq. 6.57): KNCnew = IGC + (1-dcorpnew)*(pKN/pKN(-1))*KNCnew(-1), with BEA 2011 initial value 98.1 (1925), BEA 1993 depreciation rate dcorpnew (from `BEA_1993_FA_methodology/BEA_1993_depreciation_retirement_rates.csv`), and IRS interwar adjustment via XS008 multiplier for 1925-1947.</t>
+          <t>KNCcorp_baseline = GPIM (eq. 6.57): KNCnew = IGC + (1-dcorpnew)*(pKN/pKN(-1))*KNCnew(-1), with BEA 2011 initial value 98.1 (1925), BEA 1993 depreciation rate dcorpnew (from the staged 1993 BEA depreciation/retirement rates), and IRS interwar adjustment via the XS008 multiplier for 1925-1947.</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>`V03_XS004_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The validation step round-trips the constructed series against the Appendix 6.8 source workbook at a 1.0% tolerance. Two data-sourcing steps needed for this construction are resolved: the remap of financial services indirectly measured (FISIM) in NIPA Table 7.11, and the 1993 BEA depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS004 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Under the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline, and following the principle that extended values must be rebuilt from sources rather than spliced, **extension does NOT splice the published XS004 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -8266,14 +8266,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>1. Fetch the BEA NIPA tables via the BEA data API (a BEA API key is required), using the table ids documented for this series' primary source.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>2. Fetch BEA Fixed Asset Tables 6.1, 6.4, 6.7, 6.8 from the same source.</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4. BEA 1993 depreciation/retirement rates are read from `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/BEA_1993_depreciation_retirement_rates.csv` (Phase 5 blocker CH6-B3 RESOLVED). Rate inputs freeze at 2011-vintage projection.</t>
+          <t>4. BEA 1993 depreciation/retirement rates are read from the staged 1993 BEA Fixed Asset methodology inputs (this data-sourcing step is resolved). Rate inputs freeze at the 2011-vintage projection.</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>For XS004, the Phase 5 round-trip validation reads `XS004_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS004, the round-trip validation reads the raw series from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Source substitutions</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Forecast vs. observed data</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the staged 1993 BEA depreciation inputs).</t>
         </is>
       </c>
     </row>
@@ -8381,35 +8381,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | The load step returns a FAIL status naming the missing file |</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | The load step records 0 rows for that subseries; validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The documented re-fetch script logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| FISIM (financial services indirectly measured) revision to NIPA Table 7.11 line numbers (affects XS003) | The Table 7.11 line resolver falls back to the nearest pinned vintage with a logged warning | Lines are re-mapped by their published stub labels; the vintage used is logged |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | The capital-stock series (XS004 and related) freeze depreciation-rate inputs at the 2011-vintage projection | Documented with the staged 1993 BEA methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Comparison with the earlier replication</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+          <t>Round-trip parity with an earlier replication is expected within tolerance for the book period. The comparison against that earlier replication's per-series output is informational only, when available.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension integrity</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension MUST re-fetch the BEA, IRS, and Federal Reserve Board (FRB) component series and re-compute the formula end-to-end; splicing the published series is forbidden. The loader caches BEA and FRED responses for 30 days (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:48:20.596680+00:00</t>
+          <t>2026-07-02T06:26:39.971885+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS004_extenbook.xlsx
+++ b/extenbooks/XS004_extenbook.xlsx
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:39.971885+00:00</t>
+          <t>2026-07-11T03:44:27.389173+00:00</t>
         </is>
       </c>
     </row>
@@ -8823,11 +8823,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8850,6 +8850,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "The operational GPIM corporate capital-stock baseline consumed by S601-S604 (net current-cost, gross current-cost, and historical-cost corporate stocks). All billions_current_usd, single-unit, renders sensibly. Appendix Table 6.8.II.5. This is the primary GPIM series; XS005-XS008 are its methodology variants.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS004_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS004_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Operational baseline used by S601-S604 (combines BEA 2011 initial + BEA 1993 depreciation + IRS interwar adjustment). Source: Appendix Table 6.8.II.5. Per Decision 0002 + Phase 4 Q6: XS004 is the operational baseline; XS005 is the pure reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>billions_current_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
